--- a/docs/ai-caiq/AI-CAIQ-ziggurat-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-ziggurat-v1.1.0.xlsx
@@ -9082,7 +9082,7 @@
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>The tool keeps no audit log of its own. WHAT DOES EXIST: a hash-chained custody ledger written by a separate tool (stop-guessing) into `.stop-guessing/ledger/custody.jsonl`, 492 records, tracked in git, each record naming a keyid for an HMAC-SHA256 chain. Two things stop that being an answer of Yes here, and both are recorded rather than smoothed over: keyed verification could not be run in this environment (the chain key is not available to the assessor, and the keyless mode reports honestly as "chain-only, never tamper-proof"), and `stop-guessing ledger verify --path &lt;file&gt;` crashes with a RecursionError, so a specific project's ledger cannot be verified at all today. The ledger is also tamper-EVIDENT, not write-protected: an attacker with the repo can rewrite history, and only the chain would show it.</t>
+          <t>The tool keeps no audit log of its own. WHAT DOES EXIST: a hash-chained custody ledger written by a separate tool (stop-guessing) into `.stop-guessing/ledger/custody.jsonl`, 492 records, tracked in git, HMAC-SHA256 under a named keyid -- and as of 2026-09-17 it verifies: "PASS: 492 records, chain intact and verified under its key". Getting that answer required fixing the verifier first (mEllergrace/stop-guessing#94 defect 1, fixed in 92208b2): `ledger verify --path` recursed until the interpreter gave up, so no per-project ledger could be verified at all. The answer stays No for a better reason than an earlier draft gave: the ledger is tamper-EVIDENT, not write-protected. Anyone with the repository can rewrite it and only the chain would show it, access to the records is not restricted (they are committed to a public repo), and three further defects in the verification surface are still open -- `doctor` and `verify` disagree about the same profile, the keyed failure message asserts tampering it has not established, and `claims check` crashes on a vendored install.</t>
         </is>
       </c>
       <c r="F229" s="14" t="n"/>
